--- a/scheme/Seta/issues_metadados_seta.xlsx
+++ b/scheme/Seta/issues_metadados_seta.xlsx
@@ -63616,7 +63616,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQMS01</t>
+          <t>MQME001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -63631,7 +63631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQMS02</t>
+          <t>MQME002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -63646,7 +63646,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQMS03</t>
+          <t>MQME003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -63661,7 +63661,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MQMS04</t>
+          <t>MQME004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -63676,7 +63676,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MQMS05</t>
+          <t>MQME005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -63747,7 +63747,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -63773,7 +63773,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -63799,7 +63799,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -63825,7 +63825,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -63851,7 +63851,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MQME10</t>
+          <t>MQME012</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -63877,7 +63877,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -63907,7 +63907,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -63937,7 +63937,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -63967,7 +63967,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -63997,7 +63997,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -64027,7 +64027,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -64057,7 +64057,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -64087,7 +64087,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -64117,7 +64117,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -64147,7 +64147,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -64177,7 +64177,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -64207,7 +64207,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -64237,7 +64237,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -64267,7 +64267,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -64297,7 +64297,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -64327,7 +64327,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -64357,7 +64357,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -64387,7 +64387,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -64417,7 +64417,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -64447,7 +64447,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -64477,7 +64477,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -64507,7 +64507,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -64537,7 +64537,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -64567,7 +64567,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -64597,7 +64597,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -64627,7 +64627,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -64657,7 +64657,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -64687,7 +64687,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -64717,7 +64717,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -64747,7 +64747,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -64777,7 +64777,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -64807,7 +64807,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -64837,7 +64837,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -64867,7 +64867,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -64897,7 +64897,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -64927,7 +64927,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -64957,7 +64957,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -64987,7 +64987,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -65017,7 +65017,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -65047,7 +65047,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -65077,7 +65077,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -65107,7 +65107,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -65137,7 +65137,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -65167,7 +65167,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -65197,7 +65197,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -65227,7 +65227,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -65257,7 +65257,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -65287,7 +65287,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -65317,7 +65317,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -65347,7 +65347,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -65377,7 +65377,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -65407,7 +65407,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -65437,7 +65437,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -65467,7 +65467,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -65497,7 +65497,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -65527,7 +65527,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -65557,7 +65557,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -65587,7 +65587,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -65617,7 +65617,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -65647,7 +65647,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -65677,7 +65677,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -65707,7 +65707,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -65737,7 +65737,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -65767,7 +65767,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -65797,7 +65797,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -65827,7 +65827,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -65857,7 +65857,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -65887,7 +65887,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -65917,7 +65917,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -65947,7 +65947,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -65977,7 +65977,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -66007,7 +66007,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -66037,7 +66037,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -66067,7 +66067,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -66097,7 +66097,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -66127,7 +66127,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -66157,7 +66157,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -66187,7 +66187,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -66217,7 +66217,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -66247,7 +66247,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -66277,7 +66277,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -66307,7 +66307,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -66337,7 +66337,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -66367,7 +66367,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -66397,7 +66397,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -66427,7 +66427,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -66457,7 +66457,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -66487,7 +66487,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -66517,7 +66517,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -66547,7 +66547,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -66577,7 +66577,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -66607,7 +66607,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -66637,7 +66637,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -66667,7 +66667,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -66697,7 +66697,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -66727,7 +66727,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -66757,7 +66757,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -66787,7 +66787,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -66817,7 +66817,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -66847,7 +66847,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -66877,7 +66877,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -66907,7 +66907,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -66937,7 +66937,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -66967,7 +66967,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -66997,7 +66997,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -67027,7 +67027,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -67057,7 +67057,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -67087,7 +67087,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -67117,7 +67117,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -67147,7 +67147,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -67177,7 +67177,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -67207,7 +67207,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -67237,7 +67237,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -67267,7 +67267,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -67297,7 +67297,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -67327,7 +67327,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -67357,7 +67357,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -67387,7 +67387,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -67417,7 +67417,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -67447,7 +67447,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -67477,7 +67477,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -67507,7 +67507,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -67537,7 +67537,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -67567,7 +67567,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -67597,7 +67597,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -67627,7 +67627,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -67657,7 +67657,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -67687,7 +67687,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -67717,7 +67717,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -67747,7 +67747,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -67777,7 +67777,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -67807,7 +67807,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -67837,7 +67837,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -67867,7 +67867,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -67897,7 +67897,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -67927,7 +67927,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -67957,7 +67957,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -67987,7 +67987,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -68017,7 +68017,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -68047,7 +68047,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -68077,7 +68077,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -68107,7 +68107,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -68137,7 +68137,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -68167,7 +68167,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -68197,7 +68197,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -68227,7 +68227,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -68257,7 +68257,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -68287,7 +68287,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -68317,7 +68317,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -68347,7 +68347,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -68377,7 +68377,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -68407,7 +68407,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -68437,7 +68437,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -68467,7 +68467,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -68497,7 +68497,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -68527,7 +68527,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -68557,7 +68557,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -68587,7 +68587,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -68617,7 +68617,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -68647,7 +68647,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -68677,7 +68677,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -68707,7 +68707,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -68737,7 +68737,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -68767,7 +68767,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -68797,7 +68797,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -68827,7 +68827,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -68857,7 +68857,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -68887,7 +68887,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -68917,7 +68917,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -68947,7 +68947,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -68977,7 +68977,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -69007,7 +69007,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -69037,7 +69037,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -69067,7 +69067,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -69097,7 +69097,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -69127,7 +69127,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -69157,7 +69157,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -69187,7 +69187,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -69217,7 +69217,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -69247,7 +69247,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -69277,7 +69277,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -69307,7 +69307,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -69337,7 +69337,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -69367,7 +69367,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -69397,7 +69397,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -69427,7 +69427,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -69457,7 +69457,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -69487,7 +69487,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -69517,7 +69517,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -69547,7 +69547,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -69577,7 +69577,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -69607,7 +69607,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -69637,7 +69637,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -69667,7 +69667,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -69697,7 +69697,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -69727,7 +69727,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -69757,7 +69757,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -69787,7 +69787,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -69817,7 +69817,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -69847,7 +69847,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -69877,7 +69877,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -69907,7 +69907,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -69937,7 +69937,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -69967,7 +69967,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -69997,7 +69997,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -70027,7 +70027,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -70057,7 +70057,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -70087,7 +70087,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -70117,7 +70117,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -70147,7 +70147,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -70177,7 +70177,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -70207,7 +70207,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -70237,7 +70237,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -70267,7 +70267,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -70297,7 +70297,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -70327,7 +70327,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -70357,7 +70357,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -70387,7 +70387,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -70417,7 +70417,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -70447,7 +70447,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -70477,7 +70477,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -70507,7 +70507,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -70537,7 +70537,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -70567,7 +70567,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -70597,7 +70597,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -70627,7 +70627,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -70657,7 +70657,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -70687,7 +70687,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -70717,7 +70717,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -70747,7 +70747,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -70777,7 +70777,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -70807,7 +70807,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -70837,7 +70837,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -70867,7 +70867,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -70897,7 +70897,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -70927,7 +70927,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -70957,7 +70957,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -70987,7 +70987,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -71017,7 +71017,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -71047,7 +71047,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -71077,7 +71077,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -71107,7 +71107,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -71137,7 +71137,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -71167,7 +71167,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -71197,7 +71197,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -71227,7 +71227,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -71257,7 +71257,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -71287,7 +71287,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -71317,7 +71317,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -71347,7 +71347,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -71377,7 +71377,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -71407,7 +71407,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -71437,7 +71437,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -71467,7 +71467,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -71497,7 +71497,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -71527,7 +71527,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -71557,7 +71557,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -71587,7 +71587,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -71617,7 +71617,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -71647,7 +71647,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -71677,7 +71677,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -71707,7 +71707,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -71737,7 +71737,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -71767,7 +71767,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -71797,7 +71797,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -71827,7 +71827,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -71857,7 +71857,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -71887,7 +71887,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -71917,7 +71917,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -71947,7 +71947,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -71977,7 +71977,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -72007,7 +72007,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -72037,7 +72037,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -72067,7 +72067,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -72097,7 +72097,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -72127,7 +72127,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -72157,7 +72157,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -72187,7 +72187,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -72217,7 +72217,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -72247,7 +72247,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -72277,7 +72277,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -72307,7 +72307,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -72337,7 +72337,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -72367,7 +72367,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -72397,7 +72397,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -72427,7 +72427,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -72457,7 +72457,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -72487,7 +72487,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -72517,7 +72517,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -72547,7 +72547,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -72577,7 +72577,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -72607,7 +72607,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -72637,7 +72637,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -72667,7 +72667,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -72697,7 +72697,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -72727,7 +72727,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -72757,7 +72757,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MQME12</t>
+          <t>MQME014</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -72787,7 +72787,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -72817,7 +72817,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -72847,7 +72847,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -72877,7 +72877,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -72907,7 +72907,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -72937,7 +72937,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -72967,7 +72967,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -72997,7 +72997,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -73027,7 +73027,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -73057,7 +73057,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -73087,7 +73087,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -73117,7 +73117,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -73147,7 +73147,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -73177,7 +73177,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -73207,7 +73207,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -73237,7 +73237,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -73267,7 +73267,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -73297,7 +73297,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -73327,7 +73327,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -73357,7 +73357,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -73387,7 +73387,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -73417,7 +73417,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -73447,7 +73447,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -73477,7 +73477,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -73507,7 +73507,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -73537,7 +73537,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -73567,7 +73567,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -73597,7 +73597,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -73627,7 +73627,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -73657,7 +73657,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -73687,7 +73687,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -73717,7 +73717,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -73747,7 +73747,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -73777,7 +73777,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -73807,7 +73807,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -73837,7 +73837,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -73867,7 +73867,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -73897,7 +73897,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -73927,7 +73927,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -73957,7 +73957,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -73987,7 +73987,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -74017,7 +74017,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -74047,7 +74047,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -74077,7 +74077,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -74107,7 +74107,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -74137,7 +74137,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -74167,7 +74167,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -74197,7 +74197,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -74227,7 +74227,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -74257,7 +74257,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -74287,7 +74287,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -74317,7 +74317,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -74347,7 +74347,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -74377,7 +74377,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -74407,7 +74407,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -74437,7 +74437,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -74467,7 +74467,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -74497,7 +74497,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -74527,7 +74527,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -74557,7 +74557,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -74587,7 +74587,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -74617,7 +74617,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -74647,7 +74647,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -74677,7 +74677,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -74707,7 +74707,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -74737,7 +74737,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -74767,7 +74767,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -74797,7 +74797,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -74827,7 +74827,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -74857,7 +74857,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -74887,7 +74887,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -74917,7 +74917,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -74947,7 +74947,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -74977,7 +74977,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -75007,7 +75007,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -75037,7 +75037,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -75067,7 +75067,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -75097,7 +75097,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -75127,7 +75127,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -75157,7 +75157,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -75187,7 +75187,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -75217,7 +75217,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -75247,7 +75247,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -75277,7 +75277,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -75307,7 +75307,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -75337,7 +75337,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -75367,7 +75367,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -75397,7 +75397,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -75427,7 +75427,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -75457,7 +75457,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -75487,7 +75487,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -75517,7 +75517,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -75547,7 +75547,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -75577,7 +75577,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -75607,7 +75607,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -75637,7 +75637,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -75667,7 +75667,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -75697,7 +75697,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -75727,7 +75727,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -75757,7 +75757,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -75787,7 +75787,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -75817,7 +75817,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -75847,7 +75847,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -75877,7 +75877,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -75907,7 +75907,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -75937,7 +75937,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -75967,7 +75967,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -75997,7 +75997,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -76027,7 +76027,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -76057,7 +76057,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -76087,7 +76087,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -76117,7 +76117,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -76147,7 +76147,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -76177,7 +76177,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -76207,7 +76207,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -76237,7 +76237,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -76267,7 +76267,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -76297,7 +76297,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -76327,7 +76327,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -76357,7 +76357,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -76387,7 +76387,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -76417,7 +76417,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -76447,7 +76447,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -76477,7 +76477,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -76507,7 +76507,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -76537,7 +76537,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -76567,7 +76567,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -76597,7 +76597,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -76627,7 +76627,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -76657,7 +76657,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -76687,7 +76687,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -76717,7 +76717,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -76747,7 +76747,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -76777,7 +76777,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -76807,7 +76807,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -76837,7 +76837,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -76867,7 +76867,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -76897,7 +76897,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -76927,7 +76927,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -76957,7 +76957,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -76987,7 +76987,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -77017,7 +77017,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -77047,7 +77047,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -77077,7 +77077,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -77107,7 +77107,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -77137,7 +77137,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -77167,7 +77167,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -77197,7 +77197,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -77227,7 +77227,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -77257,7 +77257,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -77287,7 +77287,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -77317,7 +77317,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -77347,7 +77347,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -77377,7 +77377,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -77407,7 +77407,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -77437,7 +77437,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -77467,7 +77467,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -77497,7 +77497,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -77527,7 +77527,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -77557,7 +77557,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -77587,7 +77587,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -77617,7 +77617,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -77647,7 +77647,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -77677,7 +77677,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -77707,7 +77707,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -77737,7 +77737,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -77767,7 +77767,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -77797,7 +77797,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -77827,7 +77827,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -77857,7 +77857,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -77887,7 +77887,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -77917,7 +77917,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -77947,7 +77947,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -77977,7 +77977,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -78007,7 +78007,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -78037,7 +78037,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -78067,7 +78067,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -78097,7 +78097,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -78127,7 +78127,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -78157,7 +78157,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -78187,7 +78187,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -78217,7 +78217,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -78247,7 +78247,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -78277,7 +78277,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -78307,7 +78307,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -78337,7 +78337,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -78367,7 +78367,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -78397,7 +78397,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -78427,7 +78427,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -78457,7 +78457,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -78487,7 +78487,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -78517,7 +78517,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -78547,7 +78547,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -78577,7 +78577,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -78607,7 +78607,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -78637,7 +78637,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -78667,7 +78667,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -78697,7 +78697,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -78727,7 +78727,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -78757,7 +78757,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -78787,7 +78787,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -78817,7 +78817,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -78847,7 +78847,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -78877,7 +78877,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -78907,7 +78907,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -78937,7 +78937,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -78967,7 +78967,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -78997,7 +78997,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -79027,7 +79027,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -79057,7 +79057,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -79087,7 +79087,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -79117,7 +79117,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -79147,7 +79147,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -79177,7 +79177,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -79207,7 +79207,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -79237,7 +79237,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -79267,7 +79267,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -79297,7 +79297,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -79327,7 +79327,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -79357,7 +79357,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -79387,7 +79387,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -79417,7 +79417,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -79447,7 +79447,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -79477,7 +79477,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -79507,7 +79507,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -79537,7 +79537,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -79567,7 +79567,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -79597,7 +79597,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -79627,7 +79627,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -79657,7 +79657,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -79687,7 +79687,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -79717,7 +79717,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -79747,7 +79747,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -79777,7 +79777,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -79807,7 +79807,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -79837,7 +79837,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -79867,7 +79867,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -79897,7 +79897,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -79927,7 +79927,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -79957,7 +79957,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -79987,7 +79987,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -80017,7 +80017,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -80047,7 +80047,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -80077,7 +80077,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -80107,7 +80107,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -80137,7 +80137,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -80167,7 +80167,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -80197,7 +80197,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -80227,7 +80227,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -80257,7 +80257,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -80287,7 +80287,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -80317,7 +80317,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -80347,7 +80347,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -80377,7 +80377,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -80407,7 +80407,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -80437,7 +80437,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -80467,7 +80467,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -80497,7 +80497,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -80527,7 +80527,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -80557,7 +80557,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -80587,7 +80587,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -80617,7 +80617,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -80647,7 +80647,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -80677,7 +80677,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -80707,7 +80707,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -80737,7 +80737,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -80767,7 +80767,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -80797,7 +80797,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -80827,7 +80827,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -80857,7 +80857,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -80887,7 +80887,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -80917,7 +80917,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -80947,7 +80947,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -80977,7 +80977,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -81007,7 +81007,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -81037,7 +81037,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -81067,7 +81067,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -81097,7 +81097,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -81127,7 +81127,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -81157,7 +81157,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -81187,7 +81187,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -81217,7 +81217,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -81247,7 +81247,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -81277,7 +81277,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -81307,7 +81307,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -81337,7 +81337,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -81367,7 +81367,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -81397,7 +81397,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -81427,7 +81427,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -81457,7 +81457,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -81487,7 +81487,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -81517,7 +81517,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -81547,7 +81547,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -81577,7 +81577,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -81607,7 +81607,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -81637,7 +81637,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -81667,7 +81667,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -81697,7 +81697,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -81727,7 +81727,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -81757,7 +81757,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -81787,7 +81787,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -81817,7 +81817,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -81847,7 +81847,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -81877,7 +81877,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -81907,7 +81907,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -81937,7 +81937,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -81967,7 +81967,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -81997,7 +81997,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -82027,7 +82027,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -82057,7 +82057,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -82087,7 +82087,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -82117,7 +82117,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -82147,7 +82147,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -82177,7 +82177,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -82207,7 +82207,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -82237,7 +82237,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -82267,7 +82267,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -82297,7 +82297,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -82327,7 +82327,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -82357,7 +82357,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -82387,7 +82387,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -82417,7 +82417,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -82447,7 +82447,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -82477,7 +82477,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -82507,7 +82507,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -82537,7 +82537,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -82567,7 +82567,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -82597,7 +82597,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -82627,7 +82627,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -82657,7 +82657,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -82687,7 +82687,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -82717,7 +82717,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -82747,7 +82747,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -82777,7 +82777,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -82807,7 +82807,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -82837,7 +82837,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -82867,7 +82867,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -82897,7 +82897,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -82927,7 +82927,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -82957,7 +82957,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -82987,7 +82987,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -83017,7 +83017,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -83047,7 +83047,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -83077,7 +83077,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -83107,7 +83107,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -83137,7 +83137,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -83167,7 +83167,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -83197,7 +83197,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -83227,7 +83227,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -83257,7 +83257,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -83287,7 +83287,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -83317,7 +83317,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -83347,7 +83347,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -83377,7 +83377,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -83407,7 +83407,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -83437,7 +83437,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -83467,7 +83467,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -83497,7 +83497,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -83527,7 +83527,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -83557,7 +83557,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -83587,7 +83587,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -83617,7 +83617,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -83647,7 +83647,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -83677,7 +83677,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -83707,7 +83707,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -83737,7 +83737,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -83767,7 +83767,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -83797,7 +83797,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -83827,7 +83827,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -83857,7 +83857,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -83887,7 +83887,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -83917,7 +83917,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -83947,7 +83947,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -83977,7 +83977,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -84007,7 +84007,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -84037,7 +84037,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -84067,7 +84067,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -84097,7 +84097,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -84127,7 +84127,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -84157,7 +84157,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -84187,7 +84187,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -84217,7 +84217,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -84247,7 +84247,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -84277,7 +84277,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -84307,7 +84307,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -84337,7 +84337,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -84367,7 +84367,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -84397,7 +84397,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -84427,7 +84427,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -84457,7 +84457,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -84487,7 +84487,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -84517,7 +84517,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -84547,7 +84547,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -84577,7 +84577,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -84607,7 +84607,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -84637,7 +84637,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -84667,7 +84667,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -84697,7 +84697,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -84727,7 +84727,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -84757,7 +84757,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -84787,7 +84787,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -84817,7 +84817,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -84847,7 +84847,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -84877,7 +84877,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -84907,7 +84907,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -84937,7 +84937,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -84967,7 +84967,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -84997,7 +84997,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -85027,7 +85027,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -85057,7 +85057,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -85087,7 +85087,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -85117,7 +85117,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -85147,7 +85147,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -85177,7 +85177,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -85207,7 +85207,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -85237,7 +85237,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -85267,7 +85267,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -85297,7 +85297,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -85327,7 +85327,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -85357,7 +85357,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -85387,7 +85387,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -85417,7 +85417,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -85447,7 +85447,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -85477,7 +85477,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -85507,7 +85507,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -85537,7 +85537,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -85567,7 +85567,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -85597,7 +85597,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -85627,7 +85627,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -85657,7 +85657,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -85687,7 +85687,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -85717,7 +85717,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -85747,7 +85747,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -85777,7 +85777,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -85807,7 +85807,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -85837,7 +85837,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -85867,7 +85867,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -85897,7 +85897,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -85927,7 +85927,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -85957,7 +85957,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -85987,7 +85987,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -86017,7 +86017,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -86047,7 +86047,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -86077,7 +86077,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -86107,7 +86107,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -86137,7 +86137,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -86167,7 +86167,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -86197,7 +86197,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -86227,7 +86227,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -86257,7 +86257,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -86287,7 +86287,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -86317,7 +86317,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -86347,7 +86347,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -86377,7 +86377,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -86407,7 +86407,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -86437,7 +86437,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -86467,7 +86467,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -86497,7 +86497,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -86527,7 +86527,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -86557,7 +86557,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -86587,7 +86587,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -86617,7 +86617,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -86647,7 +86647,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -86677,7 +86677,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -86707,7 +86707,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -86737,7 +86737,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -86767,7 +86767,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -86797,7 +86797,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -86827,7 +86827,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -86857,7 +86857,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -86887,7 +86887,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -86917,7 +86917,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -86947,7 +86947,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -86977,7 +86977,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -87007,7 +87007,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -87037,7 +87037,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -87067,7 +87067,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -87097,7 +87097,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -87127,7 +87127,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -87157,7 +87157,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -87187,7 +87187,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -87217,7 +87217,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -87247,7 +87247,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -87277,7 +87277,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -87307,7 +87307,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -87337,7 +87337,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -87367,7 +87367,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -87397,7 +87397,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -87427,7 +87427,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -87457,7 +87457,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -87487,7 +87487,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -87517,7 +87517,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -87547,7 +87547,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -87577,7 +87577,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -87607,7 +87607,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -87637,7 +87637,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -87667,7 +87667,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -87697,7 +87697,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -87727,7 +87727,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -87757,7 +87757,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -87787,7 +87787,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -87817,7 +87817,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -87847,7 +87847,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -87877,7 +87877,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -87907,7 +87907,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -87937,7 +87937,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -87967,7 +87967,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -87997,7 +87997,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -88027,7 +88027,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -88057,7 +88057,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -88087,7 +88087,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -88117,7 +88117,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -88147,7 +88147,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -88177,7 +88177,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -88207,7 +88207,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -88237,7 +88237,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -88267,7 +88267,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -88297,7 +88297,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -88327,7 +88327,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -88357,7 +88357,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -88387,7 +88387,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -88417,7 +88417,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -88447,7 +88447,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -88477,7 +88477,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -88507,7 +88507,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -88537,7 +88537,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -88567,7 +88567,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -88597,7 +88597,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -88627,7 +88627,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -88657,7 +88657,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -88687,7 +88687,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -88717,7 +88717,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -88747,7 +88747,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -88777,7 +88777,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -88807,7 +88807,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -88837,7 +88837,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -88867,7 +88867,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -88897,7 +88897,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -88927,7 +88927,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -88957,7 +88957,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -88987,7 +88987,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -89017,7 +89017,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -89047,7 +89047,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -89077,7 +89077,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -89107,7 +89107,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -89137,7 +89137,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -89167,7 +89167,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -89197,7 +89197,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -89227,7 +89227,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -89257,7 +89257,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -89287,7 +89287,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -89317,7 +89317,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -89347,7 +89347,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -89377,7 +89377,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -89407,7 +89407,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -89437,7 +89437,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -89467,7 +89467,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -89497,7 +89497,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -89527,7 +89527,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -89557,7 +89557,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -89587,7 +89587,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -89617,7 +89617,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -89647,7 +89647,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>MQME01</t>
+          <t>MQME008</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -89677,7 +89677,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -89711,7 +89711,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -89745,7 +89745,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -89779,7 +89779,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -89813,7 +89813,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -89847,7 +89847,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -89881,7 +89881,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -89915,7 +89915,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -89949,7 +89949,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -89983,7 +89983,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -90017,7 +90017,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -90051,7 +90051,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -90085,7 +90085,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -90119,7 +90119,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -90153,7 +90153,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -90187,7 +90187,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -90221,7 +90221,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -90255,7 +90255,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -90289,7 +90289,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -90323,7 +90323,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -90357,7 +90357,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -90391,7 +90391,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -90425,7 +90425,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -90459,7 +90459,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -90493,7 +90493,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -90527,7 +90527,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -90561,7 +90561,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -90595,7 +90595,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -90629,7 +90629,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -90663,7 +90663,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -90697,7 +90697,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -90731,7 +90731,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -90765,7 +90765,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -90799,7 +90799,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -90833,7 +90833,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -90867,7 +90867,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -90901,7 +90901,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -90935,7 +90935,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -90969,7 +90969,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -91003,7 +91003,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -91037,7 +91037,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -91071,7 +91071,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -91105,7 +91105,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -91139,7 +91139,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -91173,7 +91173,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -91207,7 +91207,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -91241,7 +91241,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -91275,7 +91275,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -91309,7 +91309,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -91343,7 +91343,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>MQME14</t>
+          <t>MQME009</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -91377,7 +91377,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -91411,7 +91411,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -91445,7 +91445,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -91479,7 +91479,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -91513,7 +91513,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -91547,7 +91547,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -91581,7 +91581,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -91615,7 +91615,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -91649,7 +91649,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -91683,7 +91683,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -91717,7 +91717,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -91751,7 +91751,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -91785,7 +91785,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -91819,7 +91819,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -91853,7 +91853,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -91887,7 +91887,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -91921,7 +91921,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -91955,7 +91955,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -91989,7 +91989,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -92023,7 +92023,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -92057,7 +92057,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -92091,7 +92091,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -92125,7 +92125,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -92159,7 +92159,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -92193,7 +92193,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -92227,7 +92227,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -92261,7 +92261,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -92295,7 +92295,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -92329,7 +92329,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -92363,7 +92363,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>MQME15</t>
+          <t>MQME010</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -92397,7 +92397,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>MQME16</t>
+          <t>MQME011</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -92431,7 +92431,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>MQME16</t>
+          <t>MQME011</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -92465,7 +92465,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>MQME16</t>
+          <t>MQME011</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -92507,7 +92507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92530,45 +92530,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MQME00</t>
+          <t>MQME006</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Total number of columns</t>
+          <t>Total number of length-required columns</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1017</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MQMEA1</t>
+          <t>MQME007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Total number of length-required columns</t>
+          <t>Total number of NUMBER columns</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MQMEA2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Total number of NUMBER columns</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
         <v>458</v>
       </c>
     </row>
@@ -92583,7 +92568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92606,29 +92591,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IQME01</t>
+          <t>MQID001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Columns with comments</t>
+          <t>Table names in singular</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>44.64%</t>
+          <t>97.21%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IQME02</t>
+          <t>MQID002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Columns with data type</t>
+          <t>Table with recommended name length</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -92640,29 +92625,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IQME03</t>
+          <t>MQID003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Length-required columns with data length</t>
+          <t>Columns with correct prefixes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>70.80%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IQME04</t>
+          <t>MQID004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NUMBER columns with valid scale</t>
+          <t>Columns with recommended name size</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -92674,49 +92659,117 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IQME05</t>
+          <t>MQID005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Columns with valid num_distinct</t>
+          <t>Columns with comments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>44.64%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IQME06</t>
+          <t>MQID006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Columns with valid num_nulls</t>
+          <t>Table with standard PK prefixes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>51.92%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IQME07</t>
+          <t>MQID007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Columns with valid density</t>
+          <t>Table with standard FK prefixes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>31.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MQID008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Table with standard UK prefixes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>70.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MQID009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NUMBER columns with valid scale</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MQID010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Columns with valid num_distinct</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MQID011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Columns with valid num_nulls</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
